--- a/Maestros2.xlsx
+++ b/Maestros2.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://anheuserbuschinbev-my.sharepoint.com/personal/29036436_ab-inbev_com/Documents/Desktop/Proyecto Comercial/scraper_cervezas/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="660" documentId="13_ncr:1_{827C747E-ED93-4D13-80CD-67192B300509}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A8FA5DE1-C874-46AE-A2F5-38D34A9CEC2D}"/>
+  <xr:revisionPtr revIDLastSave="687" documentId="13_ncr:1_{827C747E-ED93-4D13-80CD-67192B300509}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AA971D09-3F43-4639-BDAD-55CD549B563B}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="0" windowWidth="9780" windowHeight="11370" xr2:uid="{A247B3AC-82E8-4004-88BF-E74F30D45F1A}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{A247B3AC-82E8-4004-88BF-E74F30D45F1A}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$1:$I$105</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$1:$I$107</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="850" uniqueCount="377">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="874" uniqueCount="382">
   <si>
     <t>Sucursal</t>
   </si>
@@ -1170,6 +1170,21 @@
   </si>
   <si>
     <t>SAIEP - NEA</t>
+  </si>
+  <si>
+    <t>Hiper Chango Mas Comodoro</t>
+  </si>
+  <si>
+    <t>eyJjYW1wYWlnbnMiOm51bGwsImNoYW5uZWwiOiIxIiwicHJpY2VUYWJsZXMiOm51bGwsInJlZ2lvbklkIjoidjIuNTRCNjY0OUVFQUE0MzhGNzM0N0JCMDM4MjdDQUM2QjQiLCJ1dG1fY2FtcGFpZ24iOm51bGwsInV0bV9zb3VyY2UiOm51bGwsInV0bWlfY2FtcGFpZ24iOm51bGwsImN1cnJlbmN5Q29kZSI6IkFSUyIsImN1cnJlbmN5U3ltYm9sIjoiJCIsImNvdW50cnlDb2RlIjoiQVJHIiwiY3VsdHVyZUluZm8iOiJlcy1BUiIsImFkbWluX2N1bHR1cmVJbmZvIjoiZXMtQVIiLCJjaGFubmVsUHJpdmFjeSI6InB1YmxpYyIsImZhY2V0cyI6ImRlbGl2ZXJ5Wm9uZXNIYXNoPTBiZmY3ZTAyMzFlNTNmYmJlMjBhMThjMDYzOTQxN2E5O3BpY2t1cFBvaW50c0hhc2g9ZDBmZTkyMTlhZDdlNjk4OTgwOTViYjAwYjEyMzQ3MzI7emlwLWNvZGU9OTAwMztjb3VudHJ5PUFSRztjb29yZGluYXRlcz0tNjcuNTIyODk2LC00NS44ODM1OTsifQ</t>
+  </si>
+  <si>
+    <t>Hiper Chango Mas Bariloche</t>
+  </si>
+  <si>
+    <t>Hiper Carrefour Comodoro Rivadavia</t>
+  </si>
+  <si>
+    <t>eyJjYW1wYWlnbnMiOm51bGwsImNoYW5uZWwiOiIxIiwicHJpY2VUYWJsZXMiOm51bGwsInJlZ2lvbklkIjoiVTFjalkyRnljbVZtYjNWeVlYSXdNamt5TzJOaGNuSmxabTkxY21GeU1EZzVPUT09IiwidXRtX2NhbXBhaWduIjpudWxsLCJ1dG1fc291cmNlIjpudWxsLCJ1dG1pX2NhbXBhaWduIjpudWxsLCJjdXJyZW5jeUNvZGUiOiJBUlMiLCJjdXJyZW5jeVN5bWJvbCI6IiQiLCJjb3VudHJ5Q29kZSI6IkFSRyIsImN1bHR1cmVJbmZvIjoiZXMtQVIiLCJhZG1pbl9jdWx0dXJlSW5mbyI6ImVzLUFSIiwiY2hhbm5lbFByaXZhY3kiOiJwdWJsaWMiLCJmYWNldHMiOiJjb3VudHJ5PUFSRztjb29yZGluYXRlcz0tNjcuNDgwMTUsIC00NS44NjE1NTM7In0</t>
   </si>
 </sst>
 </file>
@@ -1271,14 +1286,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
@@ -1615,7 +1629,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{505DB70D-69A3-4653-8000-ED51A5396FF8}">
-  <dimension ref="A1:I105"/>
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:I108"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="32.69921875" bestFit="1" customWidth="1"/>
@@ -1654,11 +1669,11 @@
       <c r="H1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="I1" s="3" t="s">
         <v>341</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>84</v>
       </c>
@@ -1687,7 +1702,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>24</v>
       </c>
@@ -1716,7 +1731,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>100</v>
       </c>
@@ -1745,7 +1760,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>146</v>
       </c>
@@ -1774,7 +1789,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>95</v>
       </c>
@@ -1803,7 +1818,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>76</v>
       </c>
@@ -1832,7 +1847,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>33</v>
       </c>
@@ -1861,7 +1876,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>33</v>
       </c>
@@ -1890,7 +1905,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>142</v>
       </c>
@@ -1919,7 +1934,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>152</v>
       </c>
@@ -1941,11 +1956,11 @@
       <c r="H11" t="s">
         <v>267</v>
       </c>
-      <c r="I11" s="7" t="s">
+      <c r="I11" s="6" t="s">
         <v>342</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>159</v>
       </c>
@@ -1967,11 +1982,11 @@
       <c r="H12" t="s">
         <v>267</v>
       </c>
-      <c r="I12" s="7" t="s">
+      <c r="I12" s="6" t="s">
         <v>342</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>173</v>
       </c>
@@ -1993,11 +2008,11 @@
       <c r="H13" t="s">
         <v>267</v>
       </c>
-      <c r="I13" s="7" t="s">
+      <c r="I13" s="6" t="s">
         <v>342</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>181</v>
       </c>
@@ -2019,11 +2034,11 @@
       <c r="H14" t="s">
         <v>267</v>
       </c>
-      <c r="I14" s="7" t="s">
+      <c r="I14" s="6" t="s">
         <v>342</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>186</v>
       </c>
@@ -2049,7 +2064,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>188</v>
       </c>
@@ -2075,7 +2090,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>201</v>
       </c>
@@ -2101,7 +2116,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="18" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>203</v>
       </c>
@@ -2127,7 +2142,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="19" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>205</v>
       </c>
@@ -2153,7 +2168,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="20" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>206</v>
       </c>
@@ -2177,7 +2192,7 @@
       </c>
       <c r="I20" s="5"/>
     </row>
-    <row r="21" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>211</v>
       </c>
@@ -2199,11 +2214,11 @@
       <c r="H21" t="s">
         <v>267</v>
       </c>
-      <c r="I21" s="7" t="s">
+      <c r="I21" s="6" t="s">
         <v>346</v>
       </c>
     </row>
-    <row r="22" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>217</v>
       </c>
@@ -2225,11 +2240,11 @@
       <c r="H22" t="s">
         <v>267</v>
       </c>
-      <c r="I22" s="7" t="s">
+      <c r="I22" s="6" t="s">
         <v>346</v>
       </c>
     </row>
-    <row r="23" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>224</v>
       </c>
@@ -2251,11 +2266,11 @@
       <c r="H23" t="s">
         <v>267</v>
       </c>
-      <c r="I23" s="7" t="s">
+      <c r="I23" s="6" t="s">
         <v>346</v>
       </c>
     </row>
-    <row r="24" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>228</v>
       </c>
@@ -2279,7 +2294,7 @@
       </c>
       <c r="I24" s="5"/>
     </row>
-    <row r="25" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>236</v>
       </c>
@@ -2301,11 +2316,11 @@
       <c r="H25" t="s">
         <v>267</v>
       </c>
-      <c r="I25" s="7" t="s">
+      <c r="I25" s="6" t="s">
         <v>342</v>
       </c>
     </row>
-    <row r="26" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>236</v>
       </c>
@@ -2327,11 +2342,11 @@
       <c r="H26" t="s">
         <v>267</v>
       </c>
-      <c r="I26" s="7" t="s">
+      <c r="I26" s="6" t="s">
         <v>342</v>
       </c>
     </row>
-    <row r="27" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>242</v>
       </c>
@@ -2357,7 +2372,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="28" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>243</v>
       </c>
@@ -2383,7 +2398,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="29" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>244</v>
       </c>
@@ -2409,7 +2424,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="30" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>255</v>
       </c>
@@ -2438,7 +2453,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="31" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>257</v>
       </c>
@@ -2467,7 +2482,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="32" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>260</v>
       </c>
@@ -2496,7 +2511,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="33" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>39</v>
       </c>
@@ -2525,7 +2540,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="34" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>44</v>
       </c>
@@ -2550,11 +2565,11 @@
       <c r="H34" t="s">
         <v>268</v>
       </c>
-      <c r="I34" s="7" t="s">
+      <c r="I34" s="6" t="s">
         <v>361</v>
       </c>
     </row>
-    <row r="35" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>49</v>
       </c>
@@ -2583,7 +2598,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="36" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>112</v>
       </c>
@@ -2612,7 +2627,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="37" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>263</v>
       </c>
@@ -2641,7 +2656,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="38" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>55</v>
       </c>
@@ -2666,11 +2681,11 @@
       <c r="H38" t="s">
         <v>273</v>
       </c>
-      <c r="I38" s="7" t="s">
+      <c r="I38" s="6" t="s">
         <v>365</v>
       </c>
     </row>
-    <row r="39" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>163</v>
       </c>
@@ -2696,7 +2711,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="40" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>193</v>
       </c>
@@ -2722,7 +2737,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>219</v>
       </c>
@@ -2745,7 +2760,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="42" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>226</v>
       </c>
@@ -2771,7 +2786,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="43" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>272</v>
       </c>
@@ -2796,11 +2811,11 @@
       <c r="H43" t="s">
         <v>273</v>
       </c>
-      <c r="I43" s="7" t="s">
+      <c r="I43" s="6" t="s">
         <v>365</v>
       </c>
     </row>
-    <row r="44" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>60</v>
       </c>
@@ -2829,7 +2844,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="45" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>168</v>
       </c>
@@ -2851,11 +2866,11 @@
       <c r="H45" t="s">
         <v>269</v>
       </c>
-      <c r="I45" s="7" t="s">
+      <c r="I45" s="6" t="s">
         <v>374</v>
       </c>
     </row>
-    <row r="46" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>197</v>
       </c>
@@ -2881,7 +2896,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>249</v>
       </c>
@@ -2904,7 +2919,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>65</v>
       </c>
@@ -2930,7 +2945,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="49" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>239</v>
       </c>
@@ -2952,11 +2967,11 @@
       <c r="H49" t="s">
         <v>270</v>
       </c>
-      <c r="I49" s="7" t="s">
+      <c r="I49" s="6" t="s">
         <v>372</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>247</v>
       </c>
@@ -2979,7 +2994,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="51" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>70</v>
       </c>
@@ -3004,11 +3019,11 @@
       <c r="H51" t="s">
         <v>268</v>
       </c>
-      <c r="I51" s="7" t="s">
+      <c r="I51" s="6" t="s">
         <v>361</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>209</v>
       </c>
@@ -3031,7 +3046,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="53" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>80</v>
       </c>
@@ -3056,11 +3071,11 @@
       <c r="H53" t="s">
         <v>287</v>
       </c>
-      <c r="I53" s="7" t="s">
+      <c r="I53" s="6" t="s">
         <v>351</v>
       </c>
     </row>
-    <row r="54" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>175</v>
       </c>
@@ -3082,11 +3097,11 @@
       <c r="H54" t="s">
         <v>287</v>
       </c>
-      <c r="I54" s="7" t="s">
+      <c r="I54" s="6" t="s">
         <v>352</v>
       </c>
     </row>
-    <row r="55" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>89</v>
       </c>
@@ -3111,11 +3126,11 @@
       <c r="H55" t="s">
         <v>276</v>
       </c>
-      <c r="I55" s="7" t="s">
+      <c r="I55" s="6" t="s">
         <v>347</v>
       </c>
     </row>
-    <row r="56" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>170</v>
       </c>
@@ -3137,11 +3152,11 @@
       <c r="H56" t="s">
         <v>276</v>
       </c>
-      <c r="I56" s="7" t="s">
+      <c r="I56" s="6" t="s">
         <v>348</v>
       </c>
     </row>
-    <row r="57" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>199</v>
       </c>
@@ -3163,11 +3178,11 @@
       <c r="H57" t="s">
         <v>276</v>
       </c>
-      <c r="I57" s="7" t="s">
+      <c r="I57" s="6" t="s">
         <v>349</v>
       </c>
     </row>
-    <row r="58" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>238</v>
       </c>
@@ -3189,11 +3204,11 @@
       <c r="H58" t="s">
         <v>276</v>
       </c>
-      <c r="I58" s="7" t="s">
+      <c r="I58" s="6" t="s">
         <v>350</v>
       </c>
     </row>
-    <row r="59" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>275</v>
       </c>
@@ -3218,11 +3233,11 @@
       <c r="H59" t="s">
         <v>276</v>
       </c>
-      <c r="I59" s="7" t="s">
+      <c r="I59" s="6" t="s">
         <v>347</v>
       </c>
     </row>
-    <row r="60" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>106</v>
       </c>
@@ -3251,7 +3266,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>214</v>
       </c>
@@ -3274,7 +3289,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="62" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>237</v>
       </c>
@@ -3296,11 +3311,11 @@
       <c r="H62" t="s">
         <v>262</v>
       </c>
-      <c r="I62" s="7" t="s">
+      <c r="I62" s="6" t="s">
         <v>357</v>
       </c>
     </row>
-    <row r="63" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>277</v>
       </c>
@@ -3329,7 +3344,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="64" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>117</v>
       </c>
@@ -3384,9 +3399,9 @@
         <v>354</v>
       </c>
     </row>
-    <row r="66" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
-        <v>190</v>
+        <v>379</v>
       </c>
       <c r="B66" t="s">
         <v>191</v>
@@ -3395,7 +3410,7 @@
         <v>11</v>
       </c>
       <c r="D66" t="s">
-        <v>190</v>
+        <v>379</v>
       </c>
       <c r="E66" t="s">
         <v>192</v>
@@ -3410,7 +3425,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="67" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>122</v>
       </c>
@@ -3435,11 +3450,11 @@
       <c r="H67" t="s">
         <v>268</v>
       </c>
-      <c r="I67" s="7" t="s">
+      <c r="I67" s="6" t="s">
         <v>361</v>
       </c>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>251</v>
       </c>
@@ -3462,7 +3477,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="69" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>280</v>
       </c>
@@ -3487,11 +3502,11 @@
       <c r="H69" t="s">
         <v>268</v>
       </c>
-      <c r="I69" s="7" t="s">
+      <c r="I69" s="6" t="s">
         <v>361</v>
       </c>
     </row>
-    <row r="70" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>17</v>
       </c>
@@ -3516,11 +3531,11 @@
       <c r="H70" t="s">
         <v>276</v>
       </c>
-      <c r="I70" s="7" t="s">
+      <c r="I70" s="6" t="s">
         <v>347</v>
       </c>
     </row>
-    <row r="71" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>127</v>
       </c>
@@ -3545,11 +3560,11 @@
       <c r="H71" t="s">
         <v>276</v>
       </c>
-      <c r="I71" s="7" t="s">
+      <c r="I71" s="6" t="s">
         <v>347</v>
       </c>
     </row>
-    <row r="72" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>132</v>
       </c>
@@ -3578,7 +3593,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="73" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>165</v>
       </c>
@@ -3600,11 +3615,11 @@
       <c r="H73" t="s">
         <v>284</v>
       </c>
-      <c r="I73" s="7" t="s">
+      <c r="I73" s="6" t="s">
         <v>369</v>
       </c>
     </row>
-    <row r="74" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>195</v>
       </c>
@@ -3626,11 +3641,11 @@
       <c r="H74" t="s">
         <v>284</v>
       </c>
-      <c r="I74" s="7" t="s">
+      <c r="I74" s="6" t="s">
         <v>370</v>
       </c>
     </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>222</v>
       </c>
@@ -3653,7 +3668,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="76" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>281</v>
       </c>
@@ -3682,7 +3697,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="77" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>137</v>
       </c>
@@ -3707,11 +3722,11 @@
       <c r="H77" t="s">
         <v>273</v>
       </c>
-      <c r="I77" s="7" t="s">
+      <c r="I77" s="6" t="s">
         <v>365</v>
       </c>
     </row>
-    <row r="78" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>177</v>
       </c>
@@ -3737,7 +3752,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="79" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>30</v>
       </c>
@@ -3762,11 +3777,11 @@
       <c r="H79" t="s">
         <v>268</v>
       </c>
-      <c r="I79" s="7" t="s">
+      <c r="I79" s="6" t="s">
         <v>361</v>
       </c>
     </row>
-    <row r="80" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>157</v>
       </c>
@@ -3792,7 +3807,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="81" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>183</v>
       </c>
@@ -3814,11 +3829,11 @@
       <c r="H81" t="s">
         <v>268</v>
       </c>
-      <c r="I81" s="7" t="s">
+      <c r="I81" s="6" t="s">
         <v>360</v>
       </c>
     </row>
-    <row r="82" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>285</v>
       </c>
@@ -3843,11 +3858,11 @@
       <c r="H82" t="s">
         <v>268</v>
       </c>
-      <c r="I82" s="7" t="s">
+      <c r="I82" s="6" t="s">
         <v>361</v>
       </c>
     </row>
-    <row r="83" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>289</v>
       </c>
@@ -3869,11 +3884,11 @@
       <c r="H83" t="s">
         <v>267</v>
       </c>
-      <c r="I83" s="7" t="s">
+      <c r="I83" s="6" t="s">
         <v>342</v>
       </c>
     </row>
-    <row r="84" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>292</v>
       </c>
@@ -3899,7 +3914,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="85" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>294</v>
       </c>
@@ -3925,7 +3940,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="86" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
         <v>295</v>
       </c>
@@ -3954,7 +3969,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="87" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
         <v>298</v>
       </c>
@@ -3983,7 +3998,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="88" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>300</v>
       </c>
@@ -4008,11 +4023,11 @@
       <c r="H88" t="s">
         <v>273</v>
       </c>
-      <c r="I88" s="7" t="s">
+      <c r="I88" s="6" t="s">
         <v>365</v>
       </c>
     </row>
-    <row r="89" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
         <v>302</v>
       </c>
@@ -4041,7 +4056,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="90" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
         <v>304</v>
       </c>
@@ -4070,7 +4085,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="91" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
         <v>307</v>
       </c>
@@ -4092,11 +4107,11 @@
       <c r="H91" t="s">
         <v>267</v>
       </c>
-      <c r="I91" s="7" t="s">
+      <c r="I91" s="6" t="s">
         <v>345</v>
       </c>
     </row>
-    <row r="92" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
         <v>306</v>
       </c>
@@ -4118,11 +4133,11 @@
       <c r="H92" t="s">
         <v>262</v>
       </c>
-      <c r="I92" s="7" t="s">
+      <c r="I92" s="6" t="s">
         <v>356</v>
       </c>
     </row>
-    <row r="93" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
         <v>309</v>
       </c>
@@ -4144,11 +4159,11 @@
       <c r="H93" t="s">
         <v>267</v>
       </c>
-      <c r="I93" s="7" t="s">
+      <c r="I93" s="6" t="s">
         <v>345</v>
       </c>
     </row>
-    <row r="94" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
         <v>310</v>
       </c>
@@ -4170,11 +4185,11 @@
       <c r="H94" t="s">
         <v>267</v>
       </c>
-      <c r="I94" s="7" t="s">
+      <c r="I94" s="6" t="s">
         <v>345</v>
       </c>
     </row>
-    <row r="95" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
         <v>311</v>
       </c>
@@ -4200,7 +4215,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="96" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
         <v>312</v>
       </c>
@@ -4222,11 +4237,11 @@
       <c r="H96" t="s">
         <v>262</v>
       </c>
-      <c r="I96" s="7" t="s">
+      <c r="I96" s="6" t="s">
         <v>356</v>
       </c>
     </row>
-    <row r="97" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
         <v>313</v>
       </c>
@@ -4248,11 +4263,11 @@
       <c r="H97" t="s">
         <v>262</v>
       </c>
-      <c r="I97" s="7" t="s">
+      <c r="I97" s="6" t="s">
         <v>356</v>
       </c>
     </row>
-    <row r="98" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
         <v>314</v>
       </c>
@@ -4274,11 +4289,11 @@
       <c r="H98" t="s">
         <v>273</v>
       </c>
-      <c r="I98" s="7" t="s">
+      <c r="I98" s="6" t="s">
         <v>364</v>
       </c>
     </row>
-    <row r="99" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
         <v>315</v>
       </c>
@@ -4300,11 +4315,11 @@
       <c r="H99" t="s">
         <v>267</v>
       </c>
-      <c r="I99" s="7" t="s">
+      <c r="I99" s="6" t="s">
         <v>345</v>
       </c>
     </row>
-    <row r="100" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
         <v>317</v>
       </c>
@@ -4326,11 +4341,11 @@
       <c r="H100" t="s">
         <v>262</v>
       </c>
-      <c r="I100" s="7" t="s">
+      <c r="I100" s="6" t="s">
         <v>356</v>
       </c>
     </row>
-    <row r="101" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
         <v>318</v>
       </c>
@@ -4352,11 +4367,11 @@
       <c r="H101" t="s">
         <v>262</v>
       </c>
-      <c r="I101" s="7" t="s">
+      <c r="I101" s="6" t="s">
         <v>356</v>
       </c>
     </row>
-    <row r="102" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
         <v>319</v>
       </c>
@@ -4378,11 +4393,11 @@
       <c r="H102" t="s">
         <v>262</v>
       </c>
-      <c r="I102" s="7" t="s">
+      <c r="I102" s="6" t="s">
         <v>356</v>
       </c>
     </row>
-    <row r="103" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
         <v>321</v>
       </c>
@@ -4408,7 +4423,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="104" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
         <v>322</v>
       </c>
@@ -4434,7 +4449,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="105" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
         <v>323</v>
       </c>
@@ -4456,27 +4471,107 @@
       <c r="H105" t="s">
         <v>288</v>
       </c>
-      <c r="I105" s="7" t="s">
+      <c r="I105" s="6" t="s">
         <v>359</v>
       </c>
     </row>
+    <row r="106" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A106" t="s">
+        <v>377</v>
+      </c>
+      <c r="B106" t="s">
+        <v>264</v>
+      </c>
+      <c r="C106" t="s">
+        <v>265</v>
+      </c>
+      <c r="D106" t="s">
+        <v>377</v>
+      </c>
+      <c r="E106" t="s">
+        <v>378</v>
+      </c>
+      <c r="G106" t="s">
+        <v>185</v>
+      </c>
+      <c r="H106" t="s">
+        <v>262</v>
+      </c>
+      <c r="I106" s="5" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="107" spans="1:9" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A107" t="s">
+        <v>190</v>
+      </c>
+      <c r="B107" t="s">
+        <v>107</v>
+      </c>
+      <c r="C107" t="s">
+        <v>107</v>
+      </c>
+      <c r="D107" t="s">
+        <v>190</v>
+      </c>
+      <c r="E107" t="s">
+        <v>378</v>
+      </c>
+      <c r="G107" t="s">
+        <v>185</v>
+      </c>
+      <c r="H107" t="s">
+        <v>262</v>
+      </c>
+      <c r="I107" s="5" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="108" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="A108" t="s">
+        <v>380</v>
+      </c>
+      <c r="B108" t="s">
+        <v>264</v>
+      </c>
+      <c r="C108" t="s">
+        <v>265</v>
+      </c>
+      <c r="D108" t="s">
+        <v>380</v>
+      </c>
+      <c r="E108" t="s">
+        <v>381</v>
+      </c>
+      <c r="G108" t="s">
+        <v>156</v>
+      </c>
+      <c r="H108" t="s">
+        <v>262</v>
+      </c>
+      <c r="I108" s="5" t="s">
+        <v>354</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I105" xr:uid="{505DB70D-69A3-4653-8000-ED51A5396FF8}"/>
+  <autoFilter ref="A1:I107" xr:uid="{505DB70D-69A3-4653-8000-ED51A5396FF8}">
+    <filterColumn colId="6">
+      <filters>
+        <filter val="CARREFOUR"/>
+      </filters>
+    </filterColumn>
+    <filterColumn colId="7">
+      <filters>
+        <filter val="CZA - SMK - 6 - PAT-NODO 2"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="87efe3ef-b277-49df-8ab6-64e9542291c1" xsi:nil="true"/>
@@ -4485,6 +4580,15 @@
     </lcf76f155ced4ddcb4097134ff3c332f>
   </documentManagement>
 </p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -4689,20 +4793,20 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8A0C36F9-3498-4138-B26D-FF2DC39797D4}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{73B0EBC3-F407-4112-B41F-F97018C9322C}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="87efe3ef-b277-49df-8ab6-64e9542291c1"/>
     <ds:schemaRef ds:uri="81846671-63f7-4e99-8d33-8c3028a17548"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8A0C36F9-3498-4138-B26D-FF2DC39797D4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
